--- a/AAII_Financials/Yearly/FCX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FCX_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>FCX</t>
   </si>
@@ -656,199 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22855000</v>
+      </c>
+      <c r="E8" s="3">
         <v>22780000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22845000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>14198000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14402000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18628000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16403000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>14830000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14607000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20001000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20921000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18010000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20880000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15521000</v>
+      </c>
+      <c r="E9" s="3">
         <v>14959000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13926000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11421000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13098000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13427000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12003000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13248000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14286000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18498000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14634000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11546000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10920000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7334000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7821000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8919000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2777000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1304000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5201000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4400000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1582000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>321000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1503000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6287000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6464000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9960000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -865,50 +877,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E12" s="3">
         <v>115000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>55000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>42000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>104000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>105000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>93000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>63000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>107000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>106000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>210000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>285000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>271000</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -948,51 +964,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-31000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>359000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>27000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-7000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-21000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4291000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13144000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5381000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>152000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>109000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>68000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1032,9 +1054,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1048,92 +1073,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>16620000</v>
+      </c>
+      <c r="E17" s="3">
         <v>15712000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14479000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11862000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13338000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13867000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12692000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17533000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28119000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20226000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15605000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12364000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11808000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>6235000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7068000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8366000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2336000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1064000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4761000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3711000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2703000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13512000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-225000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5316000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5646000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9072000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1150,218 +1182,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>286000</v>
+      </c>
+      <c r="E20" s="3">
         <v>207000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-105000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>59000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-138000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>76000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-14000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>31000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>115000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>27000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>58000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>8589000</v>
+      </c>
+      <c r="E21" s="3">
         <v>9294000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10259000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3923000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2338000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6591000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5417000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-107000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10014000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3669000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8228000</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10056000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>515000</v>
+      </c>
+      <c r="E22" s="3">
         <v>560000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>602000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>598000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>620000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>945000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>801000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>755000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>617000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>606000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>518000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>186000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>312000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>6006000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6715000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7659000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1797000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>306000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3892000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2902000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3472000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14128000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-800000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4913000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5487000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8818000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2270000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2267000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2299000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>944000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>510000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1114000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1276000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>371000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1951000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>225000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1475000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1510000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3087000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1401,93 +1449,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3736000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4448000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5360000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>853000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-204000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2778000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1626000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3843000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12177000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1025000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3438000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3977000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5731000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1842000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3461000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4299000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>596000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-242000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2490000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1358000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3901000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12248000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1420000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2658000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3041000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4560000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1527,41 +1584,44 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>3000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>108000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>455000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-256000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>12000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>112000</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>24</v>
@@ -1569,9 +1629,12 @@
       <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1611,9 +1674,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1653,93 +1719,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-286000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-207000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>105000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-59000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>138000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-76000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>14000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-31000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-115000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-27000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-58000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1842000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3461000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4299000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>596000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-239000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2598000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1813000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4157000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12236000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1308000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2658000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3041000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4560000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1779,98 +1854,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1842000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3461000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4299000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>596000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-239000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2598000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1813000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4157000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12236000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1308000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2658000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3041000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4560000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1887,8 +1971,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1905,50 +1990,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4758000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8146000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8068000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3657000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2020000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4217000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4526000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4245000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>177000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>464000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1985000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3705000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4822000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1988,303 +2077,327 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1664000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1795000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1742000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1412000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1101000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1319000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1514000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1975000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2776000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3511000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2562000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1629000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1142000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6060000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5180000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4497000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3893000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4073000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4759000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4149000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3642000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4075000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5361000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5018000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5715000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5158000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1583000</v>
+      </c>
+      <c r="E45" s="3">
         <v>492000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>523000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>341000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>721000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>425000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>945000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>573000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1258000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1319000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>407000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>387000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>214000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14065000</v>
+      </c>
+      <c r="E46" s="3">
         <v>15613000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14830000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9303000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7915000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10720000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10626000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10435000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7462000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9045000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9972000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10297000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10047000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>316000</v>
+        <v>277000</v>
       </c>
       <c r="E47" s="3">
         <v>316000</v>
       </c>
       <c r="F47" s="3">
+        <v>316000</v>
+      </c>
+      <c r="G47" s="3">
         <v>401000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>621000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>576000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>707000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>432000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>801000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>592000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>441000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1899000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1333000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35295000</v>
+      </c>
+      <c r="E48" s="3">
         <v>32627000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30345000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>29818000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29584000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28010000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>45928000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23293000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57589000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>80901000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>47401000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20999000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26620000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>422000</v>
+      </c>
+      <c r="E49" s="3">
         <v>416000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>412000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>401000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>436000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>398000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>307000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>305000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>316000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>334000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2296000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>334000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>325000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2324,9 +2437,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2366,51 +2482,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2447000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2121000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2119000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2221000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2253000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2512000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6347000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2852000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10796000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7485000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3363000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2680000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3792000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2450,51 +2572,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>52506000</v>
+      </c>
+      <c r="E54" s="3">
         <v>51093000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>48022000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>42144000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>40809000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42216000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37302000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37317000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>46577000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>58674000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>63473000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35440000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32070000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2511,8 +2639,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2529,260 +2658,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2826000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3055000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2322000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1820000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1857000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1806000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1490000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1580000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5450000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6083000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2144000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1568000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1353000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>766000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1037000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>372000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>34000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1414000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1232000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>649000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>478000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>312000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2223000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2253000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3198000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1563000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1347000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1506000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2333000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1453000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1471000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2336000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2317000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1773000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1583000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5815000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6345000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5892000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3417000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3209000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3329000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4914000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4265000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4307000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5172000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4773000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3343000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2940000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8656000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9583000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9078000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9677000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9821000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11124000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11815000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14795000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19675000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18371000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20394000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3525000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3533000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10725000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10294000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10033000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10382000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10331000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9871000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11417000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9000000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10563000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13767000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12359000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8905000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8499000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2822,9 +2970,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2864,9 +3015,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2906,51 +3060,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35813000</v>
+      </c>
+      <c r="E66" s="3">
         <v>35538000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>34042000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31970000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31511000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32418000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29325000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>31266000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>38749000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>40387000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>42539000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17897000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16428000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2967,8 +3127,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3008,9 +3169,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3050,9 +3214,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3092,9 +3259,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3134,51 +3304,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2059000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3907000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-7375000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11681000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-12280000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12041000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14722000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-16540000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-12387000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>128000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2742000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2399000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>546000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3218,9 +3394,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3260,9 +3439,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3302,51 +3484,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16693000</v>
+      </c>
+      <c r="E76" s="3">
         <v>15555000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13980000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10174000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9298000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9798000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7977000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6051000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7828000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18287000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20934000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17543000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15642000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3386,98 +3574,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1842000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3461000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4299000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>596000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-239000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2598000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1813000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4157000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12236000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1308000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2658000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3041000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4560000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3494,50 +3691,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2068000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2019000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1998000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1528000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1412000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1754000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1714000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2610000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3497000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3863000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2797000</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>926000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3577,9 +3778,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3619,9 +3823,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3661,9 +3868,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3703,9 +3913,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3745,51 +3958,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5279000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5139000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7715000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3017000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1482000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3863000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4666000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3737000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3220000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5631000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6139000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3774000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6620000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3806,50 +4025,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4624000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3315000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2115000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1961000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2652000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1971000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1410000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2813000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6353000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7215000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5286000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3494000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2534000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3889,9 +4112,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3931,51 +4157,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4956000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3440000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1964000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1264000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2103000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5018000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3553000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6246000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3801000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10908000</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2535000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3992,50 +4224,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-863000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-866000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-331000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-73000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-291000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-218000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-6000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-605000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1305000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2281000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1129000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1423000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4075,9 +4311,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4117,9 +4356,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4159,65 +4401,71 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2650000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1623000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1340000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-128000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1556000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>900000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3055000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3166000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2786000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3351000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3049000</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3001000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>24</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -4226,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-45000</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>24</v>
@@ -4243,49 +4491,55 @@
       <c r="O101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2327000</v>
+      </c>
+      <c r="E102" s="3">
         <v>76000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4411000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1625000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2177000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-255000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>290000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4079000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-240000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1521000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1117000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1084000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FCX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FCX_YR_FIN.xlsx
@@ -974,7 +974,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>114000</v>
+        <v>183000</v>
       </c>
       <c r="E14" s="3">
         <v>-31000</v>
@@ -1080,7 +1080,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>16620000</v>
+        <v>16689000</v>
       </c>
       <c r="E17" s="3">
         <v>15712000</v>
@@ -1125,7 +1125,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>6235000</v>
+        <v>6166000</v>
       </c>
       <c r="E18" s="3">
         <v>7068000</v>
@@ -1189,7 +1189,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>286000</v>
+        <v>355000</v>
       </c>
       <c r="E20" s="3">
         <v>207000</v>
@@ -1729,7 +1729,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-286000</v>
+        <v>-355000</v>
       </c>
       <c r="E32" s="3">
         <v>-207000</v>

--- a/AAII_Financials/Yearly/FCX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FCX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>FCX</t>
   </si>
@@ -775,25 +775,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>15521000</v>
+        <v>13627000</v>
       </c>
       <c r="E9" s="3">
-        <v>14959000</v>
+        <v>13070000</v>
       </c>
       <c r="F9" s="3">
-        <v>13926000</v>
+        <v>11940000</v>
       </c>
       <c r="G9" s="3">
-        <v>11421000</v>
+        <v>10127000</v>
       </c>
       <c r="H9" s="3">
-        <v>13098000</v>
+        <v>11713000</v>
       </c>
       <c r="I9" s="3">
-        <v>13427000</v>
+        <v>11698000</v>
       </c>
       <c r="J9" s="3">
-        <v>12003000</v>
+        <v>9939000</v>
       </c>
       <c r="K9" s="3">
         <v>13248000</v>
@@ -820,25 +820,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7334000</v>
+        <v>9228000</v>
       </c>
       <c r="E10" s="3">
-        <v>7821000</v>
+        <v>9710000</v>
       </c>
       <c r="F10" s="3">
-        <v>8919000</v>
+        <v>10905000</v>
       </c>
       <c r="G10" s="3">
-        <v>2777000</v>
+        <v>4071000</v>
       </c>
       <c r="H10" s="3">
-        <v>1304000</v>
+        <v>2689000</v>
       </c>
       <c r="I10" s="3">
-        <v>5201000</v>
+        <v>6930000</v>
       </c>
       <c r="J10" s="3">
-        <v>4400000</v>
+        <v>6464000</v>
       </c>
       <c r="K10" s="3">
         <v>1582000</v>
@@ -883,26 +883,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>137000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>115000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>55000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>42000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>104000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>105000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>93000</v>
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K12" s="3">
         <v>63000</v>
@@ -974,25 +974,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>183000</v>
+        <v>-10000</v>
       </c>
       <c r="E14" s="3">
-        <v>-31000</v>
+        <v>-60000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="G14" s="3">
-        <v>359000</v>
+        <v>-207000</v>
       </c>
       <c r="H14" s="3">
-        <v>27000</v>
+        <v>-312000</v>
       </c>
       <c r="I14" s="3">
-        <v>-7000</v>
+        <v>191000</v>
       </c>
       <c r="J14" s="3">
-        <v>-21000</v>
+        <v>375000</v>
       </c>
       <c r="K14" s="3">
         <v>4291000</v>
@@ -1019,25 +1019,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2068000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2019000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1998000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1528000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1412000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1754000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1714000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,25 +1080,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>16689000</v>
+        <v>16671000</v>
       </c>
       <c r="E17" s="3">
-        <v>15712000</v>
+        <v>15725000</v>
       </c>
       <c r="F17" s="3">
-        <v>14479000</v>
+        <v>14460000</v>
       </c>
       <c r="G17" s="3">
-        <v>11862000</v>
+        <v>12125000</v>
       </c>
       <c r="H17" s="3">
-        <v>13338000</v>
+        <v>13781000</v>
       </c>
       <c r="I17" s="3">
-        <v>13867000</v>
+        <v>14100000</v>
       </c>
       <c r="J17" s="3">
-        <v>12692000</v>
+        <v>12470000</v>
       </c>
       <c r="K17" s="3">
         <v>17533000</v>
@@ -1125,25 +1125,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>6166000</v>
+        <v>6184000</v>
       </c>
       <c r="E18" s="3">
-        <v>7068000</v>
+        <v>7055000</v>
       </c>
       <c r="F18" s="3">
-        <v>8366000</v>
+        <v>8385000</v>
       </c>
       <c r="G18" s="3">
-        <v>2336000</v>
+        <v>2073000</v>
       </c>
       <c r="H18" s="3">
-        <v>1064000</v>
+        <v>621000</v>
       </c>
       <c r="I18" s="3">
-        <v>4761000</v>
+        <v>4528000</v>
       </c>
       <c r="J18" s="3">
-        <v>3711000</v>
+        <v>3933000</v>
       </c>
       <c r="K18" s="3">
         <v>-2703000</v>
@@ -1189,25 +1189,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>355000</v>
+        <v>-342000</v>
       </c>
       <c r="E20" s="3">
-        <v>207000</v>
+        <v>-186000</v>
       </c>
       <c r="F20" s="3">
-        <v>-105000</v>
+        <v>107000</v>
       </c>
       <c r="G20" s="3">
-        <v>59000</v>
+        <v>-92000</v>
       </c>
       <c r="H20" s="3">
+        <v>73000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-138000</v>
       </c>
-      <c r="I20" s="3">
-        <v>76000</v>
-      </c>
       <c r="J20" s="3">
-        <v>-8000</v>
+        <v>-10000</v>
       </c>
       <c r="K20" s="3">
         <v>-14000</v>
@@ -1234,25 +1234,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>8589000</v>
+        <v>8594000</v>
       </c>
       <c r="E21" s="3">
-        <v>9294000</v>
+        <v>9260000</v>
       </c>
       <c r="F21" s="3">
-        <v>10259000</v>
+        <v>10276000</v>
       </c>
       <c r="G21" s="3">
-        <v>3923000</v>
+        <v>3693000</v>
       </c>
       <c r="H21" s="3">
-        <v>2338000</v>
+        <v>1960000</v>
       </c>
       <c r="I21" s="3">
-        <v>6591000</v>
+        <v>6420000</v>
       </c>
       <c r="J21" s="3">
-        <v>5417000</v>
+        <v>5657000</v>
       </c>
       <c r="K21" s="3">
         <v>-107000</v>
@@ -1282,22 +1282,22 @@
         <v>515000</v>
       </c>
       <c r="E22" s="3">
-        <v>560000</v>
+        <v>555000</v>
       </c>
       <c r="F22" s="3">
-        <v>602000</v>
+        <v>559000</v>
       </c>
       <c r="G22" s="3">
-        <v>598000</v>
+        <v>563000</v>
       </c>
       <c r="H22" s="3">
-        <v>620000</v>
+        <v>542000</v>
       </c>
       <c r="I22" s="3">
-        <v>945000</v>
+        <v>575000</v>
       </c>
       <c r="J22" s="3">
-        <v>801000</v>
+        <v>656000</v>
       </c>
       <c r="K22" s="3">
         <v>755000</v>
@@ -1324,25 +1324,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>6006000</v>
+        <v>6021000</v>
       </c>
       <c r="E23" s="3">
-        <v>6715000</v>
+        <v>6746000</v>
       </c>
       <c r="F23" s="3">
-        <v>7659000</v>
+        <v>7664000</v>
       </c>
       <c r="G23" s="3">
-        <v>1797000</v>
+        <v>1809000</v>
       </c>
       <c r="H23" s="3">
-        <v>306000</v>
+        <v>318000</v>
       </c>
       <c r="I23" s="3">
-        <v>3892000</v>
+        <v>3900000</v>
       </c>
       <c r="J23" s="3">
-        <v>2902000</v>
+        <v>2912000</v>
       </c>
       <c r="K23" s="3">
         <v>-3472000</v>
@@ -1384,10 +1384,10 @@
         <v>510000</v>
       </c>
       <c r="I24" s="3">
-        <v>1114000</v>
+        <v>991000</v>
       </c>
       <c r="J24" s="3">
-        <v>1276000</v>
+        <v>883000</v>
       </c>
       <c r="K24" s="3">
         <v>371000</v>
@@ -1459,25 +1459,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>3736000</v>
+        <v>3751000</v>
       </c>
       <c r="E26" s="3">
-        <v>4448000</v>
+        <v>4479000</v>
       </c>
       <c r="F26" s="3">
-        <v>5360000</v>
+        <v>5365000</v>
       </c>
       <c r="G26" s="3">
-        <v>853000</v>
+        <v>865000</v>
       </c>
       <c r="H26" s="3">
-        <v>-204000</v>
+        <v>-192000</v>
       </c>
       <c r="I26" s="3">
-        <v>2778000</v>
+        <v>2909000</v>
       </c>
       <c r="J26" s="3">
-        <v>1626000</v>
+        <v>2029000</v>
       </c>
       <c r="K26" s="3">
         <v>-3843000</v>
@@ -1519,10 +1519,10 @@
         <v>-242000</v>
       </c>
       <c r="I27" s="3">
-        <v>2490000</v>
+        <v>2598000</v>
       </c>
       <c r="J27" s="3">
-        <v>1358000</v>
+        <v>1813000</v>
       </c>
       <c r="K27" s="3">
         <v>-3901000</v>
@@ -1593,11 +1593,11 @@
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1609,10 +1609,10 @@
         <v>3000</v>
       </c>
       <c r="I29" s="3">
-        <v>108000</v>
+        <v>-15000</v>
       </c>
       <c r="J29" s="3">
-        <v>455000</v>
+        <v>62000</v>
       </c>
       <c r="K29" s="3">
         <v>-256000</v>
@@ -1729,25 +1729,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-355000</v>
+        <v>342000</v>
       </c>
       <c r="E32" s="3">
-        <v>-207000</v>
+        <v>186000</v>
       </c>
       <c r="F32" s="3">
-        <v>105000</v>
+        <v>-107000</v>
       </c>
       <c r="G32" s="3">
-        <v>-59000</v>
+        <v>92000</v>
       </c>
       <c r="H32" s="3">
+        <v>-73000</v>
+      </c>
+      <c r="I32" s="3">
         <v>138000</v>
       </c>
-      <c r="I32" s="3">
-        <v>-76000</v>
-      </c>
       <c r="J32" s="3">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="K32" s="3">
         <v>14000</v>
@@ -1774,25 +1774,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1842000</v>
+        <v>1848000</v>
       </c>
       <c r="E33" s="3">
-        <v>3461000</v>
+        <v>3468000</v>
       </c>
       <c r="F33" s="3">
-        <v>4299000</v>
+        <v>4306000</v>
       </c>
       <c r="G33" s="3">
-        <v>596000</v>
+        <v>599000</v>
       </c>
       <c r="H33" s="3">
         <v>-239000</v>
       </c>
       <c r="I33" s="3">
-        <v>2598000</v>
+        <v>2602000</v>
       </c>
       <c r="J33" s="3">
-        <v>1813000</v>
+        <v>1817000</v>
       </c>
       <c r="K33" s="3">
         <v>-4157000</v>
@@ -1864,25 +1864,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1842000</v>
+        <v>1848000</v>
       </c>
       <c r="E35" s="3">
-        <v>3461000</v>
+        <v>3468000</v>
       </c>
       <c r="F35" s="3">
-        <v>4299000</v>
+        <v>4306000</v>
       </c>
       <c r="G35" s="3">
-        <v>596000</v>
+        <v>599000</v>
       </c>
       <c r="H35" s="3">
         <v>-239000</v>
       </c>
       <c r="I35" s="3">
-        <v>2598000</v>
+        <v>2602000</v>
       </c>
       <c r="J35" s="3">
-        <v>1813000</v>
+        <v>1817000</v>
       </c>
       <c r="K35" s="3">
         <v>-4157000</v>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>52000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2099,13 +2099,13 @@
         <v>1412000</v>
       </c>
       <c r="H43" s="3">
-        <v>1101000</v>
+        <v>1167000</v>
       </c>
       <c r="I43" s="3">
-        <v>1319000</v>
+        <v>1322000</v>
       </c>
       <c r="J43" s="3">
-        <v>1514000</v>
+        <v>1665000</v>
       </c>
       <c r="K43" s="3">
         <v>1975000</v>
@@ -2147,7 +2147,7 @@
         <v>4073000</v>
       </c>
       <c r="I44" s="3">
-        <v>4759000</v>
+        <v>4503000</v>
       </c>
       <c r="J44" s="3">
         <v>4149000</v>
@@ -2177,25 +2177,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1583000</v>
+        <v>375000</v>
       </c>
       <c r="E45" s="3">
-        <v>492000</v>
+        <v>381000</v>
       </c>
       <c r="F45" s="3">
-        <v>523000</v>
+        <v>409000</v>
       </c>
       <c r="G45" s="3">
-        <v>341000</v>
+        <v>244000</v>
       </c>
       <c r="H45" s="3">
-        <v>721000</v>
+        <v>555000</v>
       </c>
       <c r="I45" s="3">
-        <v>425000</v>
+        <v>312000</v>
       </c>
       <c r="J45" s="3">
-        <v>945000</v>
+        <v>182000</v>
       </c>
       <c r="K45" s="3">
         <v>573000</v>
@@ -2237,7 +2237,7 @@
         <v>7915000</v>
       </c>
       <c r="I46" s="3">
-        <v>10720000</v>
+        <v>10464000</v>
       </c>
       <c r="J46" s="3">
         <v>10626000</v>
@@ -2267,25 +2267,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>277000</v>
+        <v>304000</v>
       </c>
       <c r="E47" s="3">
+        <v>262000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>232000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>295000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>303000</v>
+      </c>
+      <c r="I47" s="3">
         <v>316000</v>
       </c>
-      <c r="F47" s="3">
-        <v>316000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>401000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>621000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>576000</v>
-      </c>
       <c r="J47" s="3">
-        <v>707000</v>
+        <v>262000</v>
       </c>
       <c r="K47" s="3">
         <v>432000</v>
@@ -2330,7 +2330,7 @@
         <v>28010000</v>
       </c>
       <c r="J48" s="3">
-        <v>45928000</v>
+        <v>22994000</v>
       </c>
       <c r="K48" s="3">
         <v>23293000</v>
@@ -2369,7 +2369,7 @@
         <v>401000</v>
       </c>
       <c r="H49" s="3">
-        <v>436000</v>
+        <v>402000</v>
       </c>
       <c r="I49" s="3">
         <v>398000</v>
@@ -2492,25 +2492,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2447000</v>
+        <v>2187000</v>
       </c>
       <c r="E52" s="3">
-        <v>2121000</v>
+        <v>2074000</v>
       </c>
       <c r="F52" s="3">
-        <v>2119000</v>
+        <v>2167000</v>
       </c>
       <c r="G52" s="3">
-        <v>2221000</v>
+        <v>2327000</v>
       </c>
       <c r="H52" s="3">
-        <v>2253000</v>
+        <v>2605000</v>
       </c>
       <c r="I52" s="3">
-        <v>2512000</v>
+        <v>3028000</v>
       </c>
       <c r="J52" s="3">
-        <v>6347000</v>
+        <v>3113000</v>
       </c>
       <c r="K52" s="3">
         <v>2852000</v>
@@ -2665,25 +2665,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2826000</v>
+        <v>2466000</v>
       </c>
       <c r="E57" s="3">
-        <v>3055000</v>
+        <v>2701000</v>
       </c>
       <c r="F57" s="3">
-        <v>2322000</v>
+        <v>2035000</v>
       </c>
       <c r="G57" s="3">
-        <v>1820000</v>
+        <v>1473000</v>
       </c>
       <c r="H57" s="3">
-        <v>1857000</v>
+        <v>1654000</v>
       </c>
       <c r="I57" s="3">
-        <v>1806000</v>
+        <v>1661000</v>
       </c>
       <c r="J57" s="3">
-        <v>1490000</v>
+        <v>1546000</v>
       </c>
       <c r="K57" s="3">
         <v>1580000</v>
@@ -2710,19 +2710,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>766000</v>
+        <v>850000</v>
       </c>
       <c r="E58" s="3">
-        <v>1037000</v>
+        <v>1075000</v>
       </c>
       <c r="F58" s="3">
-        <v>372000</v>
+        <v>410000</v>
       </c>
       <c r="G58" s="3">
-        <v>34000</v>
+        <v>72000</v>
       </c>
       <c r="H58" s="3">
-        <v>5000</v>
+        <v>49000</v>
       </c>
       <c r="I58" s="3">
         <v>17000</v>
@@ -2755,25 +2755,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2223000</v>
+        <v>1464000</v>
       </c>
       <c r="E59" s="3">
-        <v>2253000</v>
+        <v>1443000</v>
       </c>
       <c r="F59" s="3">
-        <v>3198000</v>
+        <v>2359000</v>
       </c>
       <c r="G59" s="3">
-        <v>1563000</v>
+        <v>799000</v>
       </c>
       <c r="H59" s="3">
-        <v>1347000</v>
+        <v>495000</v>
       </c>
       <c r="I59" s="3">
-        <v>1506000</v>
+        <v>559000</v>
       </c>
       <c r="J59" s="3">
-        <v>2333000</v>
+        <v>814000</v>
       </c>
       <c r="K59" s="3">
         <v>1453000</v>
@@ -2845,19 +2845,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8656000</v>
+        <v>9003000</v>
       </c>
       <c r="E61" s="3">
-        <v>9583000</v>
+        <v>9877000</v>
       </c>
       <c r="F61" s="3">
-        <v>9078000</v>
+        <v>9359000</v>
       </c>
       <c r="G61" s="3">
-        <v>9677000</v>
+        <v>9867000</v>
       </c>
       <c r="H61" s="3">
-        <v>9821000</v>
+        <v>10025000</v>
       </c>
       <c r="I61" s="3">
         <v>11124000</v>
@@ -2890,25 +2890,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10725000</v>
+        <v>5221000</v>
       </c>
       <c r="E62" s="3">
-        <v>10294000</v>
+        <v>4956000</v>
       </c>
       <c r="F62" s="3">
-        <v>10033000</v>
+        <v>4673000</v>
       </c>
       <c r="G62" s="3">
-        <v>10382000</v>
+        <v>4571000</v>
       </c>
       <c r="H62" s="3">
-        <v>10331000</v>
+        <v>4599000</v>
       </c>
       <c r="I62" s="3">
-        <v>9871000</v>
+        <v>4665000</v>
       </c>
       <c r="J62" s="3">
-        <v>11417000</v>
+        <v>4460000</v>
       </c>
       <c r="K62" s="3">
         <v>9000000</v>
@@ -3070,25 +3070,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>35813000</v>
+        <v>25196000</v>
       </c>
       <c r="E66" s="3">
-        <v>35538000</v>
+        <v>26222000</v>
       </c>
       <c r="F66" s="3">
-        <v>34042000</v>
+        <v>25003000</v>
       </c>
       <c r="G66" s="3">
-        <v>31970000</v>
+        <v>23476000</v>
       </c>
       <c r="H66" s="3">
-        <v>31511000</v>
+        <v>23361000</v>
       </c>
       <c r="I66" s="3">
-        <v>32418000</v>
+        <v>24324000</v>
       </c>
       <c r="J66" s="3">
-        <v>29325000</v>
+        <v>26006000</v>
       </c>
       <c r="K66" s="3">
         <v>31266000</v>
@@ -3634,25 +3634,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1842000</v>
+        <v>1848000</v>
       </c>
       <c r="E81" s="3">
-        <v>3461000</v>
+        <v>3468000</v>
       </c>
       <c r="F81" s="3">
-        <v>4299000</v>
+        <v>4306000</v>
       </c>
       <c r="G81" s="3">
-        <v>596000</v>
+        <v>599000</v>
       </c>
       <c r="H81" s="3">
         <v>-239000</v>
       </c>
       <c r="I81" s="3">
-        <v>2598000</v>
+        <v>2602000</v>
       </c>
       <c r="J81" s="3">
-        <v>1813000</v>
+        <v>1817000</v>
       </c>
       <c r="K81" s="3">
         <v>-4157000</v>
@@ -4032,10 +4032,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4624000</v>
+        <v>-4824000</v>
       </c>
       <c r="E91" s="3">
-        <v>-3315000</v>
+        <v>-3469000</v>
       </c>
       <c r="F91" s="3">
         <v>-2115000</v>
@@ -4231,25 +4231,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-863000</v>
+        <v>863000</v>
       </c>
       <c r="E96" s="3">
-        <v>-866000</v>
+        <v>866000</v>
       </c>
       <c r="F96" s="3">
-        <v>-331000</v>
+        <v>331000</v>
       </c>
       <c r="G96" s="3">
-        <v>-73000</v>
+        <v>73000</v>
       </c>
       <c r="H96" s="3">
-        <v>-291000</v>
+        <v>291000</v>
       </c>
       <c r="I96" s="3">
-        <v>-218000</v>
+        <v>218000</v>
       </c>
       <c r="J96" s="3">
-        <v>-2000</v>
+        <v>2000</v>
       </c>
       <c r="K96" s="3">
         <v>-6000</v>
@@ -4455,26 +4455,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K101" s="3">
         <v>-45000</v>

--- a/AAII_Financials/Yearly/FCX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FCX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>FCX</t>
   </si>
@@ -656,211 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25455000</v>
+      </c>
+      <c r="E8" s="3">
         <v>22855000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22780000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22845000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14198000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14402000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>18628000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16403000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14830000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14607000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20001000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20921000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18010000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20880000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>13627000</v>
+        <v>15388000</v>
       </c>
       <c r="E9" s="3">
+        <v>13560000</v>
+      </c>
+      <c r="F9" s="3">
         <v>13070000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11940000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10127000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11713000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11698000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9939000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13248000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14286000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18498000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14634000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11546000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10920000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9228000</v>
+        <v>10067000</v>
       </c>
       <c r="E10" s="3">
+        <v>9295000</v>
+      </c>
+      <c r="F10" s="3">
         <v>9710000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10905000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4071000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2689000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6930000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6464000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1582000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>321000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1503000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6287000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6464000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9960000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +890,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,27 +917,30 @@
       <c r="J12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3">
         <v>63000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>107000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>106000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>210000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>285000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>271000</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -967,81 +983,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-10000</v>
+        <v>71000</v>
       </c>
       <c r="E14" s="3">
-        <v>-60000</v>
+        <v>185000</v>
       </c>
       <c r="F14" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="G14" s="3">
         <v>55000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-207000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-312000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>191000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>375000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4291000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13144000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5381000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>152000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>109000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>68000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2068000</v>
+        <v>2310000</v>
       </c>
       <c r="E15" s="3">
+        <v>2135000</v>
+      </c>
+      <c r="F15" s="3">
         <v>2019000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1998000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1528000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1412000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1754000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1714000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1057,9 +1079,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1074,98 +1099,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>16671000</v>
+        <v>18514000</v>
       </c>
       <c r="E17" s="3">
-        <v>15725000</v>
+        <v>16606000</v>
       </c>
       <c r="F17" s="3">
+        <v>15769000</v>
+      </c>
+      <c r="G17" s="3">
         <v>14460000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12125000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13781000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14100000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12470000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17533000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28119000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20226000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15605000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12364000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11808000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>6184000</v>
+        <v>6941000</v>
       </c>
       <c r="E18" s="3">
-        <v>7055000</v>
+        <v>6249000</v>
       </c>
       <c r="F18" s="3">
+        <v>7011000</v>
+      </c>
+      <c r="G18" s="3">
         <v>8385000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2073000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>621000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4528000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3933000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2703000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13512000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-225000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5316000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5646000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9072000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1183,233 +1215,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-342000</v>
+        <v>-371000</v>
       </c>
       <c r="E20" s="3">
-        <v>-186000</v>
+        <v>-411000</v>
       </c>
       <c r="F20" s="3">
+        <v>-262000</v>
+      </c>
+      <c r="G20" s="3">
         <v>107000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-92000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>73000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-138000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-14000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>31000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>115000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>27000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>58000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>8594000</v>
+        <v>9622000</v>
       </c>
       <c r="E21" s="3">
-        <v>9260000</v>
+        <v>8795000</v>
       </c>
       <c r="F21" s="3">
+        <v>9292000</v>
+      </c>
+      <c r="G21" s="3">
         <v>10276000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3693000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1960000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6420000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5657000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-107000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10014000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3669000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8228000</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10056000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>515000</v>
+        <v>319000</v>
       </c>
       <c r="E22" s="3">
-        <v>555000</v>
+        <v>454000</v>
       </c>
       <c r="F22" s="3">
+        <v>560000</v>
+      </c>
+      <c r="G22" s="3">
         <v>559000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>563000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>542000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>575000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>656000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>755000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>617000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>606000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>518000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>186000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>312000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>6922000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6021000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6746000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7664000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1809000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>318000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3900000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2912000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3472000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14128000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-800000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4913000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5487000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8818000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2523000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2270000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2267000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2299000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>944000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>510000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>991000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>883000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>371000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1951000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>225000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1475000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1510000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3087000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1452,99 +1500,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>4399000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3751000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4479000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5365000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>865000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-192000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2909000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2029000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3843000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12177000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1025000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3438000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3977000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5731000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1883000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1842000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3461000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4299000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>596000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-242000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2598000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1813000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3901000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12248000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1420000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2658000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3041000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4560000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1587,9 +1644,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1606,25 +1666,25 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>3000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-15000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>62000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-256000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>12000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>112000</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>24</v>
@@ -1632,9 +1692,12 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1677,9 +1740,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1722,99 +1788,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>342000</v>
+        <v>371000</v>
       </c>
       <c r="E32" s="3">
-        <v>186000</v>
+        <v>411000</v>
       </c>
       <c r="F32" s="3">
+        <v>262000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-107000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>92000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-73000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>138000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>14000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-31000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-115000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-27000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-58000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1889000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1848000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3468000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4306000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>599000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-239000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2602000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1817000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4157000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12236000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1308000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2658000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3041000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4560000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1857,104 +1932,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1889000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1848000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3468000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4306000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>599000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-239000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2602000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1817000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4157000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12236000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1308000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2658000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3041000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4560000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1972,8 +2056,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1991,53 +2076,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3923000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4758000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8146000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8068000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3657000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2020000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4217000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4526000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4245000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>177000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>464000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1985000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3705000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4822000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2060,11 +2149,11 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>52000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2080,324 +2169,348 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1142000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1664000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1795000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1742000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1412000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1167000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1322000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1665000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1975000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2776000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3511000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2562000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1629000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1142000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6808000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6060000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5180000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4497000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3893000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4073000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4503000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4149000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3642000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4075000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5361000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5018000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5715000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5158000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>535000</v>
+      </c>
+      <c r="E45" s="3">
         <v>375000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>381000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>409000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>244000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>555000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>312000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>182000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>573000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1258000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1319000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>407000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>387000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>214000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13296000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14065000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15613000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14830000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9303000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7915000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10464000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10626000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10435000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7462000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9045000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9972000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10297000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10047000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>304000</v>
+        <v>456000</v>
       </c>
       <c r="E47" s="3">
+        <v>207000</v>
+      </c>
+      <c r="F47" s="3">
         <v>262000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>232000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>295000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>303000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>316000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>262000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>432000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>801000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>592000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>441000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1899000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1333000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38514000</v>
+      </c>
+      <c r="E48" s="3">
         <v>35295000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32627000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30345000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29818000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29584000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28010000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22994000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23293000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>57589000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>80901000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>47401000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20999000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26620000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E49" s="3">
         <v>422000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>416000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>412000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>401000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>402000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>398000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>307000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>305000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>316000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>334000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2296000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>334000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>325000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2440,9 +2553,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2485,54 +2601,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2187000</v>
+        <v>2154000</v>
       </c>
       <c r="E52" s="3">
+        <v>2284000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2074000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2167000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2327000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2605000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3028000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3113000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2852000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10796000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7485000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3363000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2680000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3792000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2575,54 +2697,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54848000</v>
+      </c>
+      <c r="E54" s="3">
         <v>52506000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>51093000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>48022000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>42144000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>40809000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42216000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37302000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37317000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>46577000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>58674000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>63473000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35440000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32070000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2640,8 +2768,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2659,278 +2788,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2789000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2466000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2701000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2035000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1473000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1654000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1661000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1546000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1580000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5450000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6083000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2144000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1568000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1353000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E58" s="3">
         <v>850000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1075000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>410000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>72000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>49000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1414000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1232000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>649000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>478000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>312000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1464000</v>
+        <v>1468000</v>
       </c>
       <c r="E59" s="3">
+        <v>1419000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1443000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2359000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>799000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>495000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>559000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>814000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1453000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1471000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2336000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2317000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1773000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1583000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5496000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5815000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6345000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5892000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3417000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3209000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3329000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4914000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4265000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4307000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5172000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4773000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3343000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2940000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9599000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9003000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9877000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9359000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9867000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10025000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11124000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11815000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14795000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19675000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18371000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20394000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3525000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3533000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5910000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5221000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4956000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4673000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4571000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4599000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4665000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4460000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9000000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10563000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13767000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12359000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8905000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8499000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2973,9 +3121,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3018,9 +3169,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3063,54 +3217,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26070000</v>
+      </c>
+      <c r="E66" s="3">
         <v>25196000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26222000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25003000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23476000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23361000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24324000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26006000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31266000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>38749000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>40387000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>42539000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17897000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16428000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3128,8 +3288,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3172,9 +3333,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3217,9 +3381,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3262,9 +3429,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3307,54 +3477,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-170000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2059000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3907000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-7375000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11681000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12280000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-12041000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-14722000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-16540000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-12387000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>128000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2742000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2399000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>546000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3397,9 +3573,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3442,9 +3621,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3487,54 +3669,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17581000</v>
+      </c>
+      <c r="E76" s="3">
         <v>16693000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15555000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13980000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10174000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9298000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9798000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7977000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6051000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7828000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18287000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20934000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17543000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15642000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3577,104 +3765,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1889000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1848000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3468000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4306000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>599000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-239000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2602000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1817000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4157000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12236000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1308000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2658000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3041000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4560000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3692,53 +3889,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2241000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2068000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2019000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1998000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1528000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1412000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1754000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1714000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2610000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3497000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3863000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2797000</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>926000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3781,9 +3982,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3826,9 +4030,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3871,9 +4078,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3916,9 +4126,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3961,54 +4174,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7160000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5279000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5139000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7715000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3017000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1482000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3863000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4666000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3737000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3220000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5631000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6139000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3774000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6620000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4026,53 +4245,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4808000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4824000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3469000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2115000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1961000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2652000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1971000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1410000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2813000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6353000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7215000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5286000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3494000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2534000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4115,9 +4338,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4160,54 +4386,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5028000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4956000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3440000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1964000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1264000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2103000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5018000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3553000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6246000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3801000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10908000</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2535000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4225,53 +4457,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>865000</v>
+      </c>
+      <c r="E96" s="3">
         <v>863000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>866000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>331000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>73000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>291000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>218000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-6000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-605000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1305000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2281000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1129000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1423000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4314,9 +4550,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4359,9 +4598,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4404,54 +4646,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3284000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2650000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1623000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1340000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-128000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1556000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>900000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3055000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3166000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2786000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3351000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3049000</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3001000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4476,11 +4724,11 @@
       <c r="J101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L101" s="3">
         <v>-45000</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>24</v>
@@ -4494,52 +4742,58 @@
       <c r="P101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1152000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2327000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>76000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4411000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1625000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2177000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-255000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>290000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4079000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-240000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1521000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1117000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1084000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FCX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FCX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>FCX</t>
   </si>
@@ -656,223 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25915000</v>
+      </c>
+      <c r="E8" s="3">
         <v>25455000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22855000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22780000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22845000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14198000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14402000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18628000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16403000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14830000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14607000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20001000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20921000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18010000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20880000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16310000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15388000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13560000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13070000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11940000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10127000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11713000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11698000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9939000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13248000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14286000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18498000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14634000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11546000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10920000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>9605000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10067000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9295000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9710000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10905000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4071000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2689000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6930000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6464000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1582000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>321000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1503000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6287000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6464000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9960000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -891,8 +903,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,27 +933,30 @@
       <c r="K12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="3">
         <v>63000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>107000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>106000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>210000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>285000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>271000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,87 +1002,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E14" s="3">
         <v>71000</v>
       </c>
-      <c r="E14" s="3">
-        <v>185000</v>
-      </c>
       <c r="F14" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-33000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>55000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-207000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-312000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>191000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>375000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4291000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13144000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5381000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>152000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>109000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>68000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>2308000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2310000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2135000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2019000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1998000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1528000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1412000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1754000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1714000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1082,9 +1104,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1100,104 +1125,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>18514000</v>
+        <v>19413000</v>
       </c>
       <c r="E17" s="3">
-        <v>16606000</v>
+        <v>18494000</v>
       </c>
       <c r="F17" s="3">
+        <v>16630000</v>
+      </c>
+      <c r="G17" s="3">
         <v>15769000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14460000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12125000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13781000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14100000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12470000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17533000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28119000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20226000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15605000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12364000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11808000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>6941000</v>
+        <v>6502000</v>
       </c>
       <c r="E18" s="3">
-        <v>6249000</v>
+        <v>6961000</v>
       </c>
       <c r="F18" s="3">
+        <v>6225000</v>
+      </c>
+      <c r="G18" s="3">
         <v>7011000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8385000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2073000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>621000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4528000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3933000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2703000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13512000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-225000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5316000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5646000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9072000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1216,248 +1248,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-371000</v>
+        <v>-224000</v>
       </c>
       <c r="E20" s="3">
-        <v>-411000</v>
+        <v>-351000</v>
       </c>
       <c r="F20" s="3">
+        <v>-301000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-262000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>107000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-92000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>73000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-138000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-14000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>31000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>115000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>27000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>58000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>9034000</v>
+      </c>
+      <c r="E21" s="3">
         <v>9622000</v>
       </c>
-      <c r="E21" s="3">
-        <v>8795000</v>
-      </c>
       <c r="F21" s="3">
+        <v>8661000</v>
+      </c>
+      <c r="G21" s="3">
         <v>9292000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10276000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3693000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1960000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6420000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5657000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-107000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10014000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3669000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8228000</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10056000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E22" s="3">
         <v>319000</v>
       </c>
-      <c r="E22" s="3">
-        <v>454000</v>
-      </c>
       <c r="F22" s="3">
+        <v>515000</v>
+      </c>
+      <c r="G22" s="3">
         <v>560000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>559000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>563000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>542000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>575000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>656000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>755000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>617000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>606000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>518000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>186000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>312000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>6373000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6922000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6021000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6746000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7664000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1809000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>318000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3900000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2912000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3472000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14128000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-800000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4913000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5487000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8818000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2221000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2523000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2270000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2267000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2299000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>944000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>510000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>991000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>883000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>371000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1951000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>225000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1475000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1510000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3087000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1503,105 +1551,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>4152000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4399000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3751000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4479000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5365000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>865000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-192000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2909000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2029000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3843000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12177000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1025000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3438000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3977000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5731000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2197000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1883000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1842000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3461000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4299000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>596000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-242000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2598000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1813000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3901000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12248000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1420000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2658000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3041000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4560000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1647,9 +1704,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1669,25 +1729,25 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>3000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-15000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>62000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-256000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>12000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>112000</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>24</v>
@@ -1695,9 +1755,12 @@
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1743,9 +1806,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1791,105 +1857,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>371000</v>
+        <v>224000</v>
       </c>
       <c r="E32" s="3">
-        <v>411000</v>
+        <v>351000</v>
       </c>
       <c r="F32" s="3">
+        <v>301000</v>
+      </c>
+      <c r="G32" s="3">
         <v>262000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-107000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>92000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-73000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>138000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>14000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-31000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-115000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-58000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2204000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1889000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1848000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3468000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4306000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>599000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-239000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2602000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1817000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4157000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12236000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1308000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2658000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3041000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4560000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1935,110 +2010,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2204000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1889000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1848000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3468000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4306000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>599000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-239000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2602000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1817000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4157000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12236000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1308000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2658000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3041000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4560000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2057,8 +2141,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2077,56 +2162,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3824000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3923000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4758000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8146000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8068000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3657000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2020000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4217000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4526000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4245000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>177000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>464000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1985000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3705000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4822000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2152,11 +2241,11 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>52000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2172,345 +2261,369 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1663000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1142000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1664000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1795000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1742000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1412000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1167000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1322000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1665000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1975000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2776000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3511000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2562000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1629000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1142000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7493000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6808000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6060000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5180000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4497000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3893000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4073000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4503000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4149000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3642000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4075000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5361000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5018000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5715000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5158000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>580000</v>
+      </c>
+      <c r="E45" s="3">
         <v>535000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>375000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>381000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>409000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>244000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>555000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>312000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>182000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>573000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1258000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1319000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>407000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>387000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>214000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13790000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13296000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14065000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15613000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14830000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9303000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7915000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10464000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10626000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10435000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7462000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9045000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9972000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10297000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10047000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>477000</v>
+      </c>
+      <c r="E47" s="3">
         <v>456000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>207000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>262000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>232000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>295000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>303000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>316000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>262000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>432000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>801000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>592000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>441000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1899000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1333000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40736000</v>
+      </c>
+      <c r="E48" s="3">
         <v>38514000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35295000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32627000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30345000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29818000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29584000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28010000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22994000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23293000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>57589000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>80901000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>47401000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20999000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26620000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>432000</v>
+      </c>
+      <c r="E49" s="3">
         <v>428000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>422000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>416000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>412000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>401000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>402000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>398000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>307000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>305000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>316000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>334000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2296000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>334000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>325000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2556,9 +2669,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2604,57 +2720,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2732000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2154000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2284000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2074000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2167000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2327000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2605000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3028000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3113000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2852000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10796000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7485000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3363000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2680000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3792000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2700,57 +2822,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58167000</v>
+      </c>
+      <c r="E54" s="3">
         <v>54848000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>52506000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>51093000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48022000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42144000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40809000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42216000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37302000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37317000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>46577000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>58674000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>63473000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35440000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32070000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2769,8 +2897,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2789,296 +2918,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2948000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2789000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2466000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2701000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2035000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1473000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1654000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1661000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1546000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1580000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5450000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6083000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2144000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1568000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1353000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>569000</v>
+      </c>
+      <c r="E58" s="3">
         <v>139000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>850000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1075000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>410000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>72000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>49000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1414000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1232000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>649000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>478000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>312000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1373000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1468000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1419000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1443000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2359000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>799000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>495000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>559000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>814000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1453000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1471000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2336000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2317000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1773000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1583000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6019000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5496000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5815000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6345000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5892000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3417000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3209000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3329000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4914000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4265000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4307000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5172000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4773000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3343000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2940000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9923000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9599000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9003000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9877000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9359000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9867000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10025000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11124000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11815000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14795000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19675000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18371000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20394000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3525000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3533000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6067000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5910000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5221000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4956000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4673000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4571000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4599000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4665000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4460000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9000000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10563000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13767000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12359000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8905000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8499000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3124,9 +3272,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3172,9 +3323,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3220,57 +3374,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27401000</v>
+      </c>
+      <c r="E66" s="3">
         <v>26070000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25196000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26222000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25003000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>23476000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23361000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24324000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26006000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31266000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>38749000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>40387000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>42539000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17897000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16428000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3289,8 +3449,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3336,9 +3497,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3384,9 +3548,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3432,9 +3599,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3480,57 +3650,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1385000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-170000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2059000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3907000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7375000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-11681000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-12280000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-12041000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-14722000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-16540000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-12387000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>128000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2742000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2399000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>546000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3576,9 +3752,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3624,9 +3803,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3672,57 +3854,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18899000</v>
+      </c>
+      <c r="E76" s="3">
         <v>17581000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16693000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15555000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13980000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10174000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9298000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9798000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7977000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6051000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7828000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18287000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20934000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17543000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15642000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3768,110 +3956,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2204000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1889000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1848000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3468000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4306000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>599000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-239000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2602000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1817000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4157000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12236000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1308000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2658000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3041000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4560000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3890,56 +4087,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2244000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2241000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2068000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2019000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1998000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1528000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1412000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1754000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1714000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2610000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3497000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3863000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2797000</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>926000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3985,9 +4186,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4033,9 +4237,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4081,9 +4288,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4129,9 +4339,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4177,57 +4390,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5610000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7160000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5279000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5139000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7715000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3017000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1482000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3863000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4666000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3737000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3220000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5631000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6139000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3774000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6620000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4246,56 +4465,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4494000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4808000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4824000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3469000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2115000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1961000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2652000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1971000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1410000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2813000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6353000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7215000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5286000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3494000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2534000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4341,9 +4564,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4389,57 +4615,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4472000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5028000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4956000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3440000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1964000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1264000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2103000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5018000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1321000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3553000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6246000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3801000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10908000</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2535000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4458,8 +4690,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4467,47 +4700,50 @@
         <v>865000</v>
       </c>
       <c r="E96" s="3">
+        <v>865000</v>
+      </c>
+      <c r="F96" s="3">
         <v>863000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>866000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>331000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>73000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>291000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>218000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-6000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-605000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1305000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2281000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1129000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1423000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4553,9 +4789,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4601,9 +4840,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4649,57 +4891,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1876000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3284000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2650000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1623000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1340000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-128000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1556000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>900000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3055000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3166000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2786000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3351000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3049000</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3001000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4727,11 +4975,11 @@
       <c r="K101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M101" s="3">
         <v>-45000</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>24</v>
@@ -4745,55 +4993,61 @@
       <c r="Q101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-738000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1152000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2327000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>76000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4411000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1625000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2177000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-255000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>290000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4079000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-240000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1521000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1720000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1117000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1084000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
